--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-observation-sur-la-grossesse.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-observation-sur-la-grossesse.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -776,8 +776,8 @@
     <t>Observation.value</t>
   </si>
   <si>
-    <t>http://hl7.org/cda/stds/core/StructureDefinition/ANY
-http://hl7.org/cda/stds/core/StructureDefinition/BLhttp://hl7.org/cda/stds/core/StructureDefinition/EDhttp://hl7.org/cda/stds/core/StructureDefinition/SThttp://hl7.org/cda/stds/core/StructureDefinition/CDhttp://hl7.org/cda/stds/core/StructureDefinition/CVhttp://hl7.org/cda/stds/core/StructureDefinition/CEhttp://hl7.org/cda/stds/core/StructureDefinition/COhttp://hl7.org/cda/stds/core/StructureDefinition/SChttp://hl7.org/cda/stds/core/StructureDefinition/IIhttp://hl7.org/cda/stds/core/StructureDefinition/TELhttp://hl7.org/cda/stds/core/StructureDefinition/ADhttp://hl7.org/cda/stds/core/StructureDefinition/ENhttp://hl7.org/cda/stds/core/StructureDefinition/INThttp://hl7.org/cda/stds/core/StructureDefinition/REALhttp://hl7.org/cda/stds/core/StructureDefinition/PQhttp://hl7.org/cda/stds/core/StructureDefinition/MOhttp://hl7.org/cda/stds/core/StructureDefinition/TShttp://hl7.org/cda/stds/core/StructureDefinition/IVL-PQhttp://hl7.org/cda/stds/core/StructureDefinition/IVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/PIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/EIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/SXPR-TShttp://hl7.org/cda/stds/core/StructureDefinition/RTO-PQ-PQ</t>
+    <t>http://hl7.org/cda/stds/core/StructureDefinition/CD
+http://hl7.org/cda/stds/core/StructureDefinition/PQhttp://hl7.org/cda/stds/core/StructureDefinition/SThttp://hl7.org/cda/stds/core/StructureDefinition/ADhttp://hl7.org/cda/stds/core/StructureDefinition/BLhttp://hl7.org/cda/stds/core/StructureDefinition/CEhttp://hl7.org/cda/stds/core/StructureDefinition/COhttp://hl7.org/cda/stds/core/StructureDefinition/CShttp://hl7.org/cda/stds/core/StructureDefinition/CVhttp://hl7.org/cda/stds/core/StructureDefinition/EDhttp://hl7.org/cda/stds/core/StructureDefinition/ENhttp://hl7.org/cda/stds/core/StructureDefinition/IIhttp://hl7.org/cda/stds/core/StructureDefinition/INThttp://hl7.org/cda/stds/core/StructureDefinition/INT-POShttp://hl7.org/cda/stds/core/StructureDefinition/MOhttp://hl7.org/cda/stds/core/StructureDefinition/ONhttp://hl7.org/cda/stds/core/StructureDefinition/PNhttp://hl7.org/cda/stds/core/StructureDefinition/REALhttp://hl7.org/cda/stds/core/StructureDefinition/SChttp://hl7.org/cda/stds/core/StructureDefinition/TELhttp://hl7.org/cda/stds/core/StructureDefinition/TNhttp://hl7.org/cda/stds/core/StructureDefinition/TShttp://hl7.org/cda/stds/core/StructureDefinition/IVL-INThttp://hl7.org/cda/stds/core/StructureDefinition/IVL-PQhttp://hl7.org/cda/stds/core/StructureDefinition/IVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/PIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/EIVL-TShttp://hl7.org/cda/stds/core/StructureDefinition/SXPR-TShttp://hl7.org/cda/stds/core/StructureDefinition/RTO-PQ-PQ</t>
   </si>
   <si>
     <t>Résultat de l’observation effectuée</t>
